--- a/Output/Acute Bout/Tables/t1_biomarkers_expanded.xlsx
+++ b/Output/Acute Bout/Tables/t1_biomarkers_expanded.xlsx
@@ -939,279 +939,279 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.62 (0.472)</t>
+          <t>7.62 (0.47)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7.80 (0.474)</t>
+          <t>7.80 (0.47)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.04 (0.478)</t>
+          <t>8.04 (0.48)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.28 (0.539)</t>
+          <t>8.28 (0.54)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.44 (0.523)</t>
+          <t>8.44 (0.52)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.22 (0.549)</t>
+          <t>8.22 (0.55)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.68 (0.498)</t>
+          <t>7.68 (0.50)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.50 (0.497)</t>
+          <t>7.50 (0.50)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.60 (0.513)</t>
+          <t>7.60 (0.51)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7.74 (0.842)</t>
+          <t>7.74 (0.84)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7.91 (0.803)</t>
+          <t>7.91 (0.80)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8.07 (0.809)</t>
+          <t>8.07 (0.81)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8.37 (0.916)</t>
+          <t>8.37 (0.92)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>8.49 (0.969)</t>
+          <t>8.49 (0.97)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>8.23 (0.864)</t>
+          <t>8.23 (0.86)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7.86 (0.868)</t>
+          <t>7.86 (0.87)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>7.73 (0.912)</t>
+          <t>7.73 (0.91)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>7.77 (0.915)</t>
+          <t>7.77 (0.91)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7.68 (0.674)</t>
+          <t>7.68 (0.67)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>7.85 (0.654)</t>
+          <t>7.85 (0.65)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>8.06 (0.654)</t>
+          <t>8.06 (0.65)</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>8.32 (0.741)</t>
+          <t>8.32 (0.74)</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>8.47 (0.770)</t>
+          <t>8.47 (0.77)</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>8.23 (0.716)</t>
+          <t>8.23 (0.72)</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.77 (0.706)</t>
+          <t>7.77 (0.71)</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7.63 (0.744)</t>
+          <t>7.63 (0.74)</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>7.69 (0.752)</t>
+          <t>7.69 (0.75)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.45 [7.30, 7.93]</t>
+          <t>7.45 (6.70, 8.50)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7.70 [7.50, 8.10]</t>
+          <t>7.70 (7.00, 8.90)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.00 [7.68, 8.40]</t>
+          <t>8.00 (7.40, 9.10)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8.30 [7.88, 8.70]</t>
+          <t>8.30 (7.30, 9.40)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8.50 [8.10, 8.80]</t>
+          <t>8.50 (7.60, 9.40)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.30 [7.80, 8.65]</t>
+          <t>8.30 (7.10, 9.20)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.60 [7.30, 8.10]</t>
+          <t>7.60 (6.80, 8.50)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.50 [7.20, 7.80]</t>
+          <t>7.50 (6.70, 8.50)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.60 [7.30, 8.00]</t>
+          <t>7.60 (6.70, 8.40)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7.80 [7.45, 8.15]</t>
+          <t>7.80 (6.00, 10.00)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8.00 [7.50, 8.30]</t>
+          <t>8.00 (6.00, 10.00)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>8.20 [7.60, 8.50]</t>
+          <t>8.20 (6.30, 10.20)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8.50 [7.70, 8.85]</t>
+          <t>8.50 (6.30, 10.30)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>8.70 [7.90, 9.10]</t>
+          <t>8.70 (6.50, 10.80)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>8.30 [7.60, 8.80]</t>
+          <t>8.30 (6.40, 10.50)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>7.80 [7.40, 8.50]</t>
+          <t>7.80 (6.00, 10.10)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>8.10 [7.15, 8.30]</t>
+          <t>8.10 (5.60, 9.60)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>8.00 [6.95, 8.30]</t>
+          <t>8.00 (5.60, 9.60)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7.70 [7.30, 8.10]</t>
+          <t>7.70 (6.00, 10.00)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>7.90 [7.50, 8.20]</t>
+          <t>7.90 (6.00, 10.00)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>8.10 [7.65, 8.50]</t>
+          <t>8.10 (6.30, 10.20)</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>8.40 [7.80, 8.75]</t>
+          <t>8.40 (6.30, 10.30)</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>8.50 [8.00, 8.90]</t>
+          <t>8.50 (6.50, 10.80)</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>8.30 [7.70, 8.70]</t>
+          <t>8.30 (6.40, 10.50)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.80 [7.40, 8.28]</t>
+          <t>7.80 (6.00, 10.10)</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>7.65 [7.18, 8.20]</t>
+          <t>7.65 (5.60, 9.60)</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>7.80 [7.15, 8.25]</t>
+          <t>7.80 (5.60, 9.60)</t>
         </is>
       </c>
     </row>
@@ -1509,142 +1509,142 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4.45 [4.00, 4.90]</t>
+          <t>4.45 (2.00, 8.60)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.50 [4.15, 4.85]</t>
+          <t>4.50 (2.40, 9.60)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.55 [5.18, 6.10]</t>
+          <t>5.55 (3.50, 12.80)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.85 [6.13, 7.53]</t>
+          <t>6.85 (3.90, 17.50)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7.60 [7.25, 9.00]</t>
+          <t>7.60 (4.40, 23.30)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.70 [6.00, 7.55]</t>
+          <t>6.70 (4.00, 21.00)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.70 [4.10, 5.75]</t>
+          <t>4.70 (3.30, 12.30)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.50 [4.10, 5.30]</t>
+          <t>4.50 (3.00, 8.00)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.90 [4.10, 5.65]</t>
+          <t>4.90 (3.00, 8.20)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4.20 [3.40, 5.40]</t>
+          <t>4.20 (2.90, 9.50)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.40 [3.55, 5.60]</t>
+          <t>4.40 (2.80, 9.30)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5.40 [4.70, 6.55]</t>
+          <t>5.40 (3.60, 11.20)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6.50 [5.65, 7.70]</t>
+          <t>6.50 (3.80, 12.30)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7.50 [6.40, 9.25]</t>
+          <t>7.50 (4.20, 14.10)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6.80 [5.50, 8.15]</t>
+          <t>6.80 (3.60, 12.20)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4.80 [3.75, 5.90]</t>
+          <t>4.80 (3.00, 9.70)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>4.60 [3.75, 5.95]</t>
+          <t>4.60 (3.00, 10.10)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>4.80 [3.93, 6.25]</t>
+          <t>4.80 (3.30, 10.80)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>4.40 [3.75, 5.05]</t>
+          <t>4.40 (2.00, 9.50)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>4.40 [3.88, 5.35]</t>
+          <t>4.40 (2.40, 9.60)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>5.50 [5.00, 6.30]</t>
+          <t>5.50 (3.50, 12.80)</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.60 [5.80, 7.60]</t>
+          <t>6.60 (3.80, 17.50)</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7.60 [7.00, 9.18]</t>
+          <t>7.60 (4.20, 23.30)</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6.70 [5.53, 7.90]</t>
+          <t>6.70 (3.60, 21.00)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.75 [4.00, 5.90]</t>
+          <t>4.75 (3.00, 12.30)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.55 [3.80, 5.83]</t>
+          <t>4.55 (3.00, 10.10)</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>4.90 [4.00, 6.10]</t>
+          <t>4.90 (3.00, 10.80)</t>
         </is>
       </c>
     </row>
@@ -1805,279 +1805,279 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>254 (70.7)</t>
+          <t>253.75 (70.66)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>264 (72.3)</t>
+          <t>263.96 (72.31)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>275 (75.5)</t>
+          <t>274.71 (75.50)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>293 (75.4)</t>
+          <t>293.46 (75.41)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>324 (98.6)</t>
+          <t>324.35 (98.58)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>312 (101)</t>
+          <t>311.96 (100.59)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>254 (77.8)</t>
+          <t>253.65 (77.77)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>233 (73.8)</t>
+          <t>233.00 (73.75)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>240 (75.6)</t>
+          <t>240.05 (75.57)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>252 (69.3)</t>
+          <t>252.09 (69.28)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>257 (72.6)</t>
+          <t>256.61 (72.59)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>271 (76.7)</t>
+          <t>271.35 (76.65)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>285 (80.3)</t>
+          <t>285.30 (80.32)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>321 (86.1)</t>
+          <t>320.59 (86.14)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>307 (84.3)</t>
+          <t>307.22 (84.32)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>256 (67.5)</t>
+          <t>256.04 (67.46)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>244 (64.2)</t>
+          <t>244.09 (64.21)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>246 (65.4)</t>
+          <t>246.48 (65.43)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>253 (69.2)</t>
+          <t>252.94 (69.23)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>260 (71.7)</t>
+          <t>260.28 (71.74)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>273 (75.3)</t>
+          <t>273.06 (75.26)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>289 (77.1)</t>
+          <t>289.47 (77.11)</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>323 (91.7)</t>
+          <t>322.51 (91.67)</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>310 (91.8)</t>
+          <t>309.59 (91.80)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>255 (72.0)</t>
+          <t>254.85 (71.99)</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>239 (68.3)</t>
+          <t>238.80 (68.34)</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>243 (69.5)</t>
+          <t>243.49 (69.54)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>238 [215, 273]</t>
+          <t>237.50 (125.00, 406.00)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>246 [213, 318]</t>
+          <t>246.00 (136.00, 415.00)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>254 [226, 338]</t>
+          <t>253.50 (149.00, 436.00)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>275 [238, 354]</t>
+          <t>275.00 (162.00, 443.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>317 [256, 384]</t>
+          <t>317.00 (130.00, 509.00)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>307 [240, 380]</t>
+          <t>307.00 (148.00, 499.00)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>234 [208, 296]</t>
+          <t>234.00 (134.00, 439.00)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>223 [197, 267]</t>
+          <t>223.00 (116.00, 418.00)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>214 [195, 255]</t>
+          <t>214.00 (112.00, 429.00)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>235 [210, 281]</t>
+          <t>235.00 (161.00, 460.00)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>239 [209, 294]</t>
+          <t>239.00 (163.00, 459.00)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>246 [228, 320]</t>
+          <t>246.00 (169.00, 486.00)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>268 [233, 335]</t>
+          <t>268.00 (174.00, 513.00)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>306 [261, 351]</t>
+          <t>305.50 (174.00, 543.00)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>296 [246, 346]</t>
+          <t>296.00 (171.00, 542.00)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>236 [207, 299]</t>
+          <t>236.00 (167.00, 456.00)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>230 [202, 288]</t>
+          <t>230.00 (161.00, 416.00)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>224 [200, 279]</t>
+          <t>224.00 (158.00, 403.00)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>235 [211, 281]</t>
+          <t>235.00 (125.00, 460.00)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>241 [210, 296]</t>
+          <t>240.50 (136.00, 459.00)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>251 [227, 330]</t>
+          <t>251.00 (149.00, 486.00)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>271 [235, 349]</t>
+          <t>271.00 (162.00, 513.00)</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>317 [255, 375]</t>
+          <t>317.00 (130.00, 543.00)</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>299 [243, 361]</t>
+          <t>298.50 (148.00, 542.00)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>235 [207, 296]</t>
+          <t>235.00 (134.00, 456.00)</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>225 [197, 275]</t>
+          <t>224.50 (116.00, 418.00)</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>224 [196, 270]</t>
+          <t>224.00 (112.00, 429.00)</t>
         </is>
       </c>
     </row>
@@ -2238,27 +2238,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.23 (0.407)</t>
+          <t>1.23 (0.41)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.31 (0.427)</t>
+          <t>1.31 (0.43)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.81 (0.635)</t>
+          <t>1.81 (0.64)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.35 (0.843)</t>
+          <t>2.35 (0.84)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.71 (0.879)</t>
+          <t>2.71 (0.88)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2268,37 +2268,37 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.42 (0.694)</t>
+          <t>1.42 (0.69)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.15 (0.463)</t>
+          <t>1.15 (0.46)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.16 (0.445)</t>
+          <t>1.16 (0.45)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.42 (0.473)</t>
+          <t>1.42 (0.47)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.48 (0.513)</t>
+          <t>1.48 (0.51)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.99 (0.683)</t>
+          <t>1.99 (0.68)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.57 (0.864)</t>
+          <t>2.57 (0.86)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2308,47 +2308,47 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.42 (0.912)</t>
+          <t>2.42 (0.91)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.50 (0.552)</t>
+          <t>1.50 (0.55)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.34 (0.446)</t>
+          <t>1.34 (0.45)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1.34 (0.460)</t>
+          <t>1.34 (0.46)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.33 (0.446)</t>
+          <t>1.33 (0.45)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.39 (0.474)</t>
+          <t>1.39 (0.47)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.90 (0.658)</t>
+          <t>1.90 (0.66)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.46 (0.851)</t>
+          <t>2.46 (0.85)</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2.84 (0.978)</t>
+          <t>2.84 (0.98)</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2358,159 +2358,159 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.46 (0.621)</t>
+          <t>1.46 (0.62)</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.25 (0.460)</t>
+          <t>1.25 (0.46)</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>1.26 (0.456)</t>
+          <t>1.26 (0.46)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.20 [0.905, 1.52]</t>
+          <t>1.20 (0.65, 1.98)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.36 [0.940, 1.71]</t>
+          <t>1.36 (0.73, 2.02)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.68 [1.32, 2.25]</t>
+          <t>1.68 (0.92, 3.50)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.20 [1.57, 3.10]</t>
+          <t>2.20 (1.19, 4.14)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.54 [2.06, 3.01]</t>
+          <t>2.54 (1.26, 4.89)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.06 [1.61, 2.68]</t>
+          <t>2.06 (0.62, 8.28)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.39 [0.945, 1.70]</t>
+          <t>1.39 (0.50, 3.78)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.08 [0.790, 1.40]</t>
+          <t>1.08 (0.57, 2.20)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05 [0.800, 1.34]</t>
+          <t>1.05 (0.67, 2.11)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.45 [1.07, 1.63]</t>
+          <t>1.45 (0.66, 2.54)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.46 [1.21, 1.71]</t>
+          <t>1.46 (0.57, 2.64)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.87 [1.55, 2.26]</t>
+          <t>1.87 (1.00, 3.88)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.57 [2.00, 2.84]</t>
+          <t>2.57 (1.27, 4.62)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.84 [2.33, 3.61]</t>
+          <t>2.84 (1.30, 5.78)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.23 [1.86, 3.03]</t>
+          <t>2.23 (1.04, 4.62)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.51 [1.21, 1.76]</t>
+          <t>1.51 (0.70, 2.97)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.22 [1.11, 1.55]</t>
+          <t>1.22 (0.56, 2.39)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1.31 [1.03, 1.57]</t>
+          <t>1.31 (0.61, 2.19)</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.34 [0.950, 1.57]</t>
+          <t>1.34 (0.65, 2.54)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.37 [0.990, 1.74]</t>
+          <t>1.37 (0.57, 2.64)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.77 [1.47, 2.26]</t>
+          <t>1.77 (0.92, 3.88)</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.24 [1.97, 3.04]</t>
+          <t>2.24 (1.19, 4.62)</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2.76 [2.23, 3.50]</t>
+          <t>2.76 (1.26, 5.78)</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2.10 [1.71, 2.86]</t>
+          <t>2.10 (0.62, 8.28)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.46 [1.05, 1.76]</t>
+          <t>1.46 (0.50, 3.78)</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.19 [0.853, 1.48]</t>
+          <t>1.19 (0.56, 2.39)</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>1.20 [0.910, 1.44]</t>
+          <t>1.20 (0.61, 2.19)</t>
         </is>
       </c>
     </row>
@@ -2671,279 +2671,279 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>71.4 (54.8)</t>
+          <t>71.43 (54.76)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>70.3 (56.5)</t>
+          <t>70.33 (56.46)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>75.1 (58.6)</t>
+          <t>75.08 (58.64)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.0 (60.9)</t>
+          <t>78.04 (60.88)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>87.6 (67.1)</t>
+          <t>87.62 (67.06)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>79.7 (67.4)</t>
+          <t>79.74 (67.40)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>70.5 (58.5)</t>
+          <t>70.48 (58.53)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>65.5 (56.3)</t>
+          <t>65.52 (56.35)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>67.2 (56.0)</t>
+          <t>67.24 (56.00)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>124 (128)</t>
+          <t>124.27 (127.62)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>119 (131)</t>
+          <t>119.33 (130.99)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>129 (130)</t>
+          <t>129.24 (130.27)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>139 (139)</t>
+          <t>138.50 (139.01)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>140 (131)</t>
+          <t>140.32 (130.61)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>135 (133)</t>
+          <t>134.55 (132.54)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>121 (123)</t>
+          <t>120.96 (122.72)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>120 (124)</t>
+          <t>119.74 (124.13)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>120 (135)</t>
+          <t>119.50 (134.67)</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>97.3 (99.9)</t>
+          <t>97.27 (99.93)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>93.2 (100)</t>
+          <t>93.20 (100.39)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>100 (101)</t>
+          <t>100.36 (101.28)</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>106 (107)</t>
+          <t>105.52 (106.99)</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>115 (107)</t>
+          <t>114.58 (106.68)</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>107 (107)</t>
+          <t>106.53 (106.88)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>95.7 (98.4)</t>
+          <t>95.72 (98.43)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>93.9 (101)</t>
+          <t>93.86 (100.55)</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>94.0 (106)</t>
+          <t>93.98 (106.11)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>54.0 [29.5, 89.0]</t>
+          <t>54.00 (11.00, 194.00)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>47.5 [28.8, 100]</t>
+          <t>47.50 (15.00, 197.00)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.5 [31.5, 102]</t>
+          <t>55.50 (12.00, 210.00)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>56.0 [34.8, 102]</t>
+          <t>56.00 (19.00, 212.00)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>67.0 [40.0, 114]</t>
+          <t>67.00 (15.00, 245.00)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>58.0 [30.0, 103]</t>
+          <t>58.00 (15.00, 253.00)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>52.0 [28.5, 91.0]</t>
+          <t>52.00 (10.00, 195.00)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>49.0 [28.0, 76.0]</t>
+          <t>49.00 (16.00, 208.00)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>53.0 [29.0, 77.0]</t>
+          <t>53.00 (14.00, 191.00)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>70.0 [37.8, 187]</t>
+          <t>70.00 (11.00, 518.00)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>71.0 [41.0, 124]</t>
+          <t>71.00 (14.00, 518.00)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>70.0 [45.0, 209]</t>
+          <t>70.00 (19.00, 509.00)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>73.0 [50.5, 173]</t>
+          <t>73.00 (24.00, 543.00)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>89.5 [50.8, 209]</t>
+          <t>89.50 (20.00, 487.00)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>78.5 [45.8, 206]</t>
+          <t>78.50 (17.00, 513.00)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>63.0 [40.5, 174]</t>
+          <t>63.00 (15.00, 476.00)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>65.0 [40.0, 173]</t>
+          <t>65.00 (13.00, 505.00)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>63.0 [42.3, 127]</t>
+          <t>63.00 (11.00, 551.00)</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>66.0 [34.0, 121]</t>
+          <t>66.00 (11.00, 518.00)</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>61.0 [30.0, 100]</t>
+          <t>61.00 (14.00, 518.00)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>62.0 [33.0, 116]</t>
+          <t>62.00 (12.00, 509.00)</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>70.0 [37.8, 124]</t>
+          <t>70.00 (19.00, 543.00)</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>70.0 [45.0, 144]</t>
+          <t>70.00 (15.00, 487.00)</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>72.0 [37.0, 122]</t>
+          <t>72.00 (15.00, 513.00)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>61.5 [31.8, 111]</t>
+          <t>61.50 (10.00, 476.00)</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>57.5 [30.5, 101]</t>
+          <t>57.50 (13.00, 505.00)</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>58.0 [31.5, 95.0]</t>
+          <t>58.00 (11.00, 551.00)</t>
         </is>
       </c>
     </row>
@@ -3104,279 +3104,279 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>69.5 (14.1)</t>
+          <t>69.46 (14.14)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>69.4 (13.5)</t>
+          <t>69.38 (13.46)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>69.3 (13.0)</t>
+          <t>69.33 (12.98)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>72.0 (13.7)</t>
+          <t>72.00 (13.70)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76.2 (14.5)</t>
+          <t>76.22 (14.48)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>76.1 (14.7)</t>
+          <t>76.09 (14.70)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>75.0 (14.6)</t>
+          <t>75.04 (14.64)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>75.0 (13.5)</t>
+          <t>74.95 (13.49)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>72.4 (14.7)</t>
+          <t>72.38 (14.75)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>68.5 (13.8)</t>
+          <t>68.52 (13.83)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>68.2 (13.0)</t>
+          <t>68.23 (13.01)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>69.8 (13.4)</t>
+          <t>69.78 (13.38)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>71.6 (13.3)</t>
+          <t>71.61 (13.35)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>74.8 (16.1)</t>
+          <t>74.78 (16.10)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>73.7 (16.0)</t>
+          <t>73.70 (15.98)</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>72.6 (15.7)</t>
+          <t>72.61 (15.68)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>71.8 (15.5)</t>
+          <t>71.78 (15.49)</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>71.9 (15.3)</t>
+          <t>71.87 (15.26)</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>69.0 (13.8)</t>
+          <t>69.00 (13.85)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>68.8 (13.1)</t>
+          <t>68.83 (13.11)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>69.6 (13.0)</t>
+          <t>69.55 (13.04)</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>71.8 (13.4)</t>
+          <t>71.81 (13.38)</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>75.5 (15.2)</t>
+          <t>75.50 (15.16)</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>74.9 (15.2)</t>
+          <t>74.89 (15.23)</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>73.8 (15.1)</t>
+          <t>73.83 (15.05)</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>73.3 (14.5)</t>
+          <t>73.30 (14.49)</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>72.1 (14.8)</t>
+          <t>72.11 (14.84)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>70.0 [59.0, 75.5]</t>
+          <t>70.00 (43.00, 102.00)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>69.0 [60.0, 74.0]</t>
+          <t>69.00 (42.00, 101.00)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>67.5 [60.0, 75.8]</t>
+          <t>67.50 (43.00, 97.00)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>73.5 [62.8, 79.3]</t>
+          <t>73.50 (45.00, 103.00)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>77.0 [66.5, 84.5]</t>
+          <t>77.00 (45.00, 105.00)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>78.0 [67.5, 84.0]</t>
+          <t>78.00 (44.00, 110.00)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>73.0 [64.0, 82.5]</t>
+          <t>73.00 (47.00, 109.00)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>75.0 [65.0, 82.0]</t>
+          <t>75.00 (55.00, 102.00)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>75.0 [61.0, 80.0]</t>
+          <t>75.00 (44.00, 103.00)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>68.0 [58.5, 76.0]</t>
+          <t>68.00 (40.00, 94.00)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>68.0 [58.5, 74.8]</t>
+          <t>68.00 (41.00, 92.00)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>68.0 [61.5, 76.5]</t>
+          <t>68.00 (43.00, 96.00)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>69.0 [64.0, 79.0]</t>
+          <t>69.00 (41.00, 94.00)</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>73.0 [64.5, 82.5]</t>
+          <t>73.00 (42.00, 107.00)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>70.0 [63.0, 82.5]</t>
+          <t>70.00 (43.00, 105.00)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>70.0 [62.0, 78.5]</t>
+          <t>70.00 (44.00, 108.00)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>69.0 [61.0, 76.5]</t>
+          <t>69.00 (39.00, 103.00)</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>69.0 [62.5, 76.0]</t>
+          <t>69.00 (42.00, 108.00)</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>69.0 [59.0, 76.0]</t>
+          <t>69.00 (40.00, 102.00)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>68.5 [60.0, 75.3]</t>
+          <t>68.50 (41.00, 101.00)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>68.0 [60.0, 76.5]</t>
+          <t>68.00 (43.00, 97.00)</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>70.0 [62.5, 79.5]</t>
+          <t>70.00 (41.00, 103.00)</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>73.5 [65.0, 83.8]</t>
+          <t>73.50 (42.00, 107.00)</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>71.5 [64.0, 84.0]</t>
+          <t>71.50 (43.00, 110.00)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>71.0 [62.3, 81.5]</t>
+          <t>71.00 (44.00, 109.00)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>72.0 [62.8, 79.0]</t>
+          <t>72.00 (39.00, 103.00)</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>69.5 [61.8, 79.3]</t>
+          <t>69.50 (42.00, 108.00)</t>
         </is>
       </c>
     </row>
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.124 (0.107)</t>
+          <t>0.12 (0.11)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.0570 (NA)</t>
+          <t>0.06 (NA)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.0430 (NA)</t>
+          <t>0.04 (NA)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.185 (0.153)</t>
+          <t>0.19 (0.15)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.187 (0.153)</t>
+          <t>0.19 (0.15)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.100 (NA)</t>
+          <t>0.10 (NA)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.113 (0.0947)</t>
+          <t>0.11 (0.09)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.163 (0.103)</t>
+          <t>0.16 (0.10)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.231 (0.143)</t>
+          <t>0.23 (0.14)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.269 (0.153)</t>
+          <t>0.27 (0.15)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3622,37 +3622,37 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.170 (0.139)</t>
+          <t>0.17 (0.14)</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.143 (0.105)</t>
+          <t>0.14 (0.11)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.0570 (NA)</t>
+          <t>0.06 (NA)</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.0430 (NA)</t>
+          <t>0.04 (NA)</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.208 (0.148)</t>
+          <t>0.21 (0.15)</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.227 (0.157)</t>
+          <t>0.23 (0.16)</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0.100 (NA)</t>
+          <t>0.10 (NA)</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -3667,149 +3667,149 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.140 (0.119)</t>
+          <t>0.14 (0.12)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.100 [0.0560, 0.160]</t>
+          <t>0.10 (0.00, 0.39)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0570 [0.0570, 0.0570]</t>
+          <t>0.06 (0.06, 0.06)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.0430 [0.0430, 0.0430]</t>
+          <t>0.04 (0.04, 0.04)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.130 [0.0885, 0.225]</t>
+          <t>0.13 (0.00, 0.54)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.165 [0.100, 0.200]</t>
+          <t>0.17 (0.00, 0.56)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.100 [0.100, 0.100]</t>
+          <t>0.10 (0.10, 0.10)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0810 [0.0550, 0.130]</t>
+          <t>0.08 (0.00, 0.30)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.145 [0.0808, 0.220]</t>
+          <t>0.15 (0.02, 0.35)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.215 [0.115, 0.318]</t>
+          <t>0.22 (0.04, 0.50)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.260 [0.120, 0.400]</t>
+          <t>0.26 (0.03, 0.47)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.110 [0.0665, 0.220]</t>
+          <t>0.11 (0.02, 0.48)</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.100 [0.0760, 0.220]</t>
+          <t>0.10 (0.00, 0.39)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.0570 [0.0570, 0.0570]</t>
+          <t>0.06 (0.06, 0.06)</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.0430 [0.0430, 0.0430]</t>
+          <t>0.04 (0.04, 0.04)</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.150 [0.0930, 0.300]</t>
+          <t>0.15 (0.00, 0.54)</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.170 [0.110, 0.360]</t>
+          <t>0.17 (0.00, 0.56)</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.100 [0.100, 0.100]</t>
+          <t>0.10 (0.10, 0.10)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.0905 [0.0573, 0.213]</t>
+          <t>0.09 (0.00, 0.48)</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.876 (0.322)</t>
+          <t>0.88 (0.32)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.880 (NA)</t>
+          <t>0.88 (NA)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.63 (0.980)</t>
+          <t>1.63 (0.98)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.813 (0.343)</t>
+          <t>0.81 (0.34)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.11 (0.354)</t>
+          <t>1.11 (0.35)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.95 (0.677)</t>
+          <t>1.95 (0.68)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2.34 (0.798)</t>
+          <t>2.34 (0.80)</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.981 (0.328)</t>
+          <t>0.98 (0.33)</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.987 (0.353)</t>
+          <t>0.99 (0.35)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.880 (NA)</t>
+          <t>0.88 (NA)</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>1.78 (0.851)</t>
+          <t>1.78 (0.85)</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4100,149 +4100,149 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.892 (0.341)</t>
+          <t>0.89 (0.34)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0.720 [0.660, 1.00]</t>
+          <t>0.72 (0.48, 1.60)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.880 [0.880, 0.880]</t>
+          <t>0.88 (0.88, 0.88)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.40 [1.40, 1.40]</t>
+          <t>1.40 (1.40, 1.40)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.30 [1.05, 1.75]</t>
+          <t>1.30 (0.89, 5.10)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.60 [1.30, 2.05]</t>
+          <t>1.60 (1.00, 8.10)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.50 [1.50, 1.50]</t>
+          <t>1.50 (1.50, 1.50)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.670 [0.590, 0.940]</t>
+          <t>0.67 (0.47, 1.60)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.10 [0.860, 1.40]</t>
+          <t>1.10 (0.49, 1.80)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.70 [1.50, 2.45]</t>
+          <t>1.70 (1.20, 3.40)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2.00 [1.70, 3.00]</t>
+          <t>2.00 (1.30, 3.90)</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.920 [0.730, 1.25]</t>
+          <t>0.92 (0.49, 1.50)</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.915 [0.718, 1.25]</t>
+          <t>0.92 (0.48, 1.80)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.880 [0.880, 0.880]</t>
+          <t>0.88 (0.88, 0.88)</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1.40 [1.40, 1.40]</t>
+          <t>1.40 (1.40, 1.40)</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>1.50 [1.20, 2.00]</t>
+          <t>1.50 (0.89, 5.10)</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1.90 [1.45, 2.65]</t>
+          <t>1.90 (1.00, 8.10)</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1.50 [1.50, 1.50]</t>
+          <t>1.50 (1.50, 1.50)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>0.805 [0.613, 1.10]</t>
+          <t>0.81 (0.47, 1.60)</t>
         </is>
       </c>
     </row>
@@ -4403,32 +4403,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.0949 (0.0557)</t>
+          <t>0.09 (0.06)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.150 (NA)</t>
+          <t>0.15 (NA)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.0750 (NA)</t>
+          <t>0.08 (NA)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.461 (0.375)</t>
+          <t>0.46 (0.37)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.598 (0.422)</t>
+          <t>0.60 (0.42)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.710 (NA)</t>
+          <t>0.71 (NA)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0775 (0.0412)</t>
+          <t>0.08 (0.04)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.119 (0.0944)</t>
+          <t>0.12 (0.09)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.456 (0.320)</t>
+          <t>0.46 (0.32)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.602 (0.424)</t>
+          <t>0.60 (0.42)</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4488,37 +4488,37 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.0788 (0.0426)</t>
+          <t>0.08 (0.04)</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.107 (0.0768)</t>
+          <t>0.11 (0.08)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.150 (NA)</t>
+          <t>0.15 (NA)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.0750 (NA)</t>
+          <t>0.08 (NA)</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.459 (0.344)</t>
+          <t>0.46 (0.34)</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.600 (0.416)</t>
+          <t>0.60 (0.42)</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>0.710 (NA)</t>
+          <t>0.71 (NA)</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4533,149 +4533,149 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>0.0781 (0.0411)</t>
+          <t>0.08 (0.04)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.0940 [0.0495, 0.128]</t>
+          <t>0.09 (0.02, 0.22)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.150 [0.150, 0.150]</t>
+          <t>0.15 (0.15, 0.15)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.0750 [0.0750, 0.0750]</t>
+          <t>0.08 (0.08, 0.08)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.290 [0.195, 0.645]</t>
+          <t>0.29 (0.05, 1.30)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.500 [0.358, 0.843]</t>
+          <t>0.50 (0.07, 1.70)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.710 [0.710, 0.710]</t>
+          <t>0.71 (0.71, 0.71)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0710 [0.0520, 0.110]</t>
+          <t>0.07 (0.01, 0.16)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.110 [0.0900, 0.130]</t>
+          <t>0.11 (0.03, 0.45)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.385 [0.233, 0.533]</t>
+          <t>0.39 (0.10, 1.30)</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.540 [0.220, 0.740]</t>
+          <t>0.54 (0.10, 1.70)</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.0830 [0.0433, 0.108]</t>
+          <t>0.08 (0.02, 0.16)</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.100 [0.0585, 0.130]</t>
+          <t>0.10 (0.02, 0.45)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>0.150 [0.150, 0.150]</t>
+          <t>0.15 (0.15, 0.15)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>0.0750 [0.0750, 0.0750]</t>
+          <t>0.08 (0.08, 0.08)</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>0.380 [0.200, 0.620]</t>
+          <t>0.38 (0.05, 1.30)</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>0.540 [0.280, 0.790]</t>
+          <t>0.54 (0.07, 1.70)</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>0.710 [0.710, 0.710]</t>
+          <t>0.71 (0.71, 0.71)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>NA [NA, NA]</t>
+          <t>NA (NA, NA)</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>0.0750 [0.0445, 0.110]</t>
+          <t>0.08 (0.01, 0.16)</t>
         </is>
       </c>
     </row>
@@ -4973,142 +4973,142 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.41 [0.623, 3.33]</t>
+          <t>1.41 (0.07, 7.37)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.15 [0.400, 2.82]</t>
+          <t>1.15 (0.07, 6.07)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.12 [0.414, 3.32]</t>
+          <t>1.12 (0.07, 8.07)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.29 [0.421, 3.73]</t>
+          <t>1.29 (0.08, 8.97)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.18 [0.407, 3.69]</t>
+          <t>1.18 (0.07, 9.28)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.12 [0.485, 3.37]</t>
+          <t>1.12 (0.08, 6.31)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.05 [0.346, 3.28]</t>
+          <t>1.05 (0.07, 8.50)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.926 [0.315, 3.21]</t>
+          <t>0.93 (0.07, 7.85)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.900 [0.386, 2.99]</t>
+          <t>0.90 (0.07, 8.06)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.47 [0.504, 6.04]</t>
+          <t>1.47 (0.02, 15.21)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.53 [0.534, 6.35]</t>
+          <t>1.53 (0.04, 15.13)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.56 [0.532, 6.30]</t>
+          <t>1.56 (0.04, 16.13)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.65 [0.581, 6.98]</t>
+          <t>1.65 (0.05, 16.74)</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.64 [0.547, 7.07]</t>
+          <t>1.64 (0.05, 15.96)</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.67 [0.782, 7.02]</t>
+          <t>1.67 (0.16, 16.59)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.43 [0.530, 6.30]</t>
+          <t>1.43 (0.04, 14.92)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.39 [0.518, 6.02]</t>
+          <t>1.39 (0.04, 13.88)</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1.31 [0.508, 6.21]</t>
+          <t>1.31 (0.04, 13.59)</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.41 [0.508, 4.56]</t>
+          <t>1.41 (0.02, 15.21)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.34 [0.479, 3.98]</t>
+          <t>1.34 (0.04, 15.13)</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.43 [0.485, 4.30]</t>
+          <t>1.43 (0.04, 16.13)</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>1.41 [0.547, 5.02]</t>
+          <t>1.41 (0.05, 16.74)</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>1.43 [0.502, 4.99]</t>
+          <t>1.43 (0.05, 15.96)</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>1.54 [0.567, 4.86]</t>
+          <t>1.54 (0.08, 16.59)</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>1.30 [0.480, 4.43]</t>
+          <t>1.30 (0.04, 14.92)</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1.21 [0.481, 3.99]</t>
+          <t>1.21 (0.04, 13.88)</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>1.23 [0.466, 3.84]</t>
+          <t>1.23 (0.04, 13.59)</t>
         </is>
       </c>
     </row>
@@ -5269,279 +5269,279 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.151 (0.106)</t>
+          <t>0.15 (0.11)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.276 (0.348)</t>
+          <t>0.28 (0.35)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.165 (0.0896)</t>
+          <t>0.16 (0.09)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0967 (0.0504)</t>
+          <t>0.10 (0.05)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.132 (0.0685)</t>
+          <t>0.13 (0.07)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.234 (0.251)</t>
+          <t>0.23 (0.25)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.142 (0.0856)</t>
+          <t>0.14 (0.09)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.134 (0.0192)</t>
+          <t>0.13 (0.02)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.116 (0.0501)</t>
+          <t>0.12 (0.05)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.107 (0.0557)</t>
+          <t>0.11 (0.06)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0.122 (0.0947)</t>
+          <t>0.12 (0.09)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0.121 (0.0575)</t>
+          <t>0.12 (0.06)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>0.105 (0.0658)</t>
+          <t>0.11 (0.07)</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0.146 (0.0859)</t>
+          <t>0.15 (0.09)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0.132 (0.0665)</t>
+          <t>0.13 (0.07)</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>0.154 (0.117)</t>
+          <t>0.15 (0.12)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>0.109 (0.0654)</t>
+          <t>0.11 (0.07)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>0.0987 (0.0400)</t>
+          <t>0.10 (0.04)</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>0.127 (0.0834)</t>
+          <t>0.13 (0.08)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>0.205 (0.266)</t>
+          <t>0.21 (0.27)</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>0.144 (0.0773)</t>
+          <t>0.14 (0.08)</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0.101 (0.0556)</t>
+          <t>0.10 (0.06)</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>0.138 (0.0743)</t>
+          <t>0.14 (0.07)</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>0.200 (0.210)</t>
+          <t>0.20 (0.21)</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>0.147 (0.0964)</t>
+          <t>0.15 (0.10)</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>0.117 (0.0545)</t>
+          <t>0.12 (0.05)</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>0.106 (0.0440)</t>
+          <t>0.11 (0.04)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.123 [0.0821, 0.186]</t>
+          <t>0.12 (0.04, 0.37)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.173 [0.112, 0.204]</t>
+          <t>0.17 (0.07, 1.06)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.146 [0.105, 0.201]</t>
+          <t>0.15 (0.05, 0.37)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0964 [0.0706, 0.132]</t>
+          <t>0.10 (0.01, 0.16)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.122 [0.0828, 0.149]</t>
+          <t>0.12 (0.06, 0.26)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.148 [0.125, 0.180]</t>
+          <t>0.15 (0.10, 0.93)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.145 [0.0756, 0.170]</t>
+          <t>0.15 (0.03, 0.33)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.134 [0.118, 0.150]</t>
+          <t>0.13 (0.12, 0.15)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.122 [0.0994, 0.129]</t>
+          <t>0.12 (0.03, 0.21)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.0909 [0.0763, 0.164]</t>
+          <t>0.09 (0.03, 0.19)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0.122 [0.0429, 0.176]</t>
+          <t>0.12 (0.02, 0.26)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0.144 [0.0816, 0.163]</t>
+          <t>0.14 (0.03, 0.19)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0.109 [0.0726, 0.159]</t>
+          <t>0.11 (0.01, 0.17)</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.129 [0.0779, 0.181]</t>
+          <t>0.13 (0.05, 0.30)</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>0.126 [0.0738, 0.167]</t>
+          <t>0.13 (0.07, 0.23)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>0.136 [0.0895, 0.162]</t>
+          <t>0.14 (0.04, 0.40)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>0.0937 [0.0559, 0.163]</t>
+          <t>0.09 (0.04, 0.21)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>0.0938 [0.0678, 0.115]</t>
+          <t>0.09 (0.04, 0.17)</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>0.119 [0.0763, 0.166]</t>
+          <t>0.12 (0.03, 0.37)</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>0.152 [0.0910, 0.203]</t>
+          <t>0.15 (0.02, 1.06)</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>0.144 [0.0935, 0.183]</t>
+          <t>0.14 (0.03, 0.37)</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>0.0964 [0.0717, 0.143]</t>
+          <t>0.10 (0.01, 0.17)</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>0.124 [0.0778, 0.159]</t>
+          <t>0.12 (0.05, 0.30)</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>0.145 [0.118, 0.178]</t>
+          <t>0.15 (0.07, 0.93)</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>0.136 [0.0821, 0.173]</t>
+          <t>0.14 (0.03, 0.40)</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>0.122 [0.0609, 0.154]</t>
+          <t>0.12 (0.04, 0.21)</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>0.103 [0.0697, 0.127]</t>
+          <t>0.10 (0.03, 0.21)</t>
         </is>
       </c>
     </row>
@@ -5702,279 +5702,279 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>294 (227)</t>
+          <t>293.89 (226.89)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>276 (227)</t>
+          <t>275.96 (227.11)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>273 (215)</t>
+          <t>273.01 (214.89)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>275 (229)</t>
+          <t>274.80 (228.80)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>288 (197)</t>
+          <t>287.77 (196.61)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>265 (162)</t>
+          <t>265.13 (162.18)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>266 (197)</t>
+          <t>265.56 (196.54)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>273 (251)</t>
+          <t>273.09 (251.38)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>281 (278)</t>
+          <t>280.70 (278.48)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>168 (112)</t>
+          <t>168.48 (111.75)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>169 (103)</t>
+          <t>169.15 (103.05)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>183 (109)</t>
+          <t>182.82 (108.90)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>181 (106)</t>
+          <t>181.23 (106.25)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>183 (107)</t>
+          <t>182.64 (106.95)</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>189 (107)</t>
+          <t>188.67 (106.72)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>170 (104)</t>
+          <t>169.86 (104.24)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>188 (118)</t>
+          <t>188.38 (117.70)</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>182 (109)</t>
+          <t>182.01 (109.30)</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>228 (185)</t>
+          <t>228.33 (185.33)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>220 (180)</t>
+          <t>220.01 (179.60)</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>227 (173)</t>
+          <t>226.87 (173.21)</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>226 (180)</t>
+          <t>225.89 (179.89)</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>231 (162)</t>
+          <t>231.36 (161.92)</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>224 (139)</t>
+          <t>223.96 (138.75)</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>216 (161)</t>
+          <t>215.54 (160.82)</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>230 (197)</t>
+          <t>229.70 (196.93)</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>225 (205)</t>
+          <t>225.34 (204.91)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>221 [147, 310]</t>
+          <t>221.46 (123.39, 939.05)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>221 [148, 308]</t>
+          <t>221.34 (77.51, 1123.98)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>228 [170, 319]</t>
+          <t>227.58 (62.30, 1115.42)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>211 [166, 311]</t>
+          <t>211.29 (59.73, 1186.07)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>247 [196, 301]</t>
+          <t>246.91 (76.14, 1018.53)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>216 [196, 287]</t>
+          <t>216.24 (97.90, 844.65)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>220 [179, 265]</t>
+          <t>219.77 (73.52, 1029.28)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>231 [191, 263]</t>
+          <t>231.50 (70.64, 1304.76)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>239 [184, 282]</t>
+          <t>238.61 (71.58, 1360.55)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>140 [100, 221]</t>
+          <t>140.12 (21.89, 490.53)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>134 [98.9, 210]</t>
+          <t>134.42 (27.13, 431.09)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>155 [112, 233]</t>
+          <t>154.58 (28.09, 444.37)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>154 [114, 241]</t>
+          <t>154.03 (26.60, 461.33)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>159 [115, 251]</t>
+          <t>158.82 (27.88, 444.23)</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>157 [111, 232]</t>
+          <t>156.90 (25.30, 445.44)</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>148 [93.6, 231]</t>
+          <t>147.92 (24.78, 467.79)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>147 [112, 252]</t>
+          <t>147.25 (25.59, 480.73)</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>151 [107, 241]</t>
+          <t>151.43 (26.50, 448.68)</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>176 [125, 261]</t>
+          <t>176.26 (21.89, 939.05)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>165 [124, 281]</t>
+          <t>164.76 (27.13, 1123.98)</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>185 [127, 267]</t>
+          <t>185.11 (28.09, 1115.42)</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>181 [123, 283]</t>
+          <t>180.95 (26.60, 1186.07)</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>210 [144, 292]</t>
+          <t>209.64 (27.88, 1018.53)</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>204 [146, 281]</t>
+          <t>203.79 (25.30, 844.65)</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>200 [113, 254]</t>
+          <t>199.59 (24.78, 1029.28)</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>208 [115, 261]</t>
+          <t>208.48 (25.59, 1304.76)</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>205 [124, 253]</t>
+          <t>205.08 (26.50, 1360.55)</t>
         </is>
       </c>
     </row>
@@ -6135,279 +6135,279 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0.232 (0.102)</t>
+          <t>0.23 (0.10)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.271 (0.0794)</t>
+          <t>0.27 (0.08)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.244 (0.0997)</t>
+          <t>0.24 (0.10)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.227 (0.106)</t>
+          <t>0.23 (0.11)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.242 (0.106)</t>
+          <t>0.24 (0.11)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.276 (0.106)</t>
+          <t>0.28 (0.11)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.241 (0.0945)</t>
+          <t>0.24 (0.09)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.240 (0.0851)</t>
+          <t>0.24 (0.09)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.209 (0.0727)</t>
+          <t>0.21 (0.07)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.277 (0.126)</t>
+          <t>0.28 (0.13)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.276 (0.136)</t>
+          <t>0.28 (0.14)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.304 (0.143)</t>
+          <t>0.30 (0.14)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.291 (0.133)</t>
+          <t>0.29 (0.13)</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.278 (0.148)</t>
+          <t>0.28 (0.15)</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>0.320 (0.136)</t>
+          <t>0.32 (0.14)</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.311 (0.120)</t>
+          <t>0.31 (0.12)</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.294 (0.122)</t>
+          <t>0.29 (0.12)</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>0.302 (0.130)</t>
+          <t>0.30 (0.13)</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>0.256 (0.116)</t>
+          <t>0.26 (0.12)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>0.274 (0.112)</t>
+          <t>0.27 (0.11)</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>0.277 (0.128)</t>
+          <t>0.28 (0.13)</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0.261 (0.123)</t>
+          <t>0.26 (0.12)</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>0.262 (0.130)</t>
+          <t>0.26 (0.13)</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>0.302 (0.124)</t>
+          <t>0.30 (0.12)</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>0.277 (0.113)</t>
+          <t>0.28 (0.11)</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.270 (0.109)</t>
+          <t>0.27 (0.11)</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>0.256 (0.114)</t>
+          <t>0.26 (0.11)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0.226 [0.168, 0.303]</t>
+          <t>0.23 (0.07, 0.40)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.233 [0.217, 0.308]</t>
+          <t>0.23 (0.19, 0.41)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.237 [0.203, 0.299]</t>
+          <t>0.24 (0.04, 0.42)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.207 [0.165, 0.271]</t>
+          <t>0.21 (0.08, 0.43)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.232 [0.160, 0.264]</t>
+          <t>0.23 (0.13, 0.50)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.266 [0.226, 0.342]</t>
+          <t>0.27 (0.09, 0.44)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.219 [0.181, 0.264]</t>
+          <t>0.22 (0.11, 0.41)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.248 [0.169, 0.283]</t>
+          <t>0.25 (0.11, 0.39)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.194 [0.177, 0.231]</t>
+          <t>0.19 (0.11, 0.36)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.242 [0.186, 0.377]</t>
+          <t>0.24 (0.11, 0.49)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.272 [0.183, 0.329]</t>
+          <t>0.27 (0.09, 0.57)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.257 [0.211, 0.351]</t>
+          <t>0.26 (0.11, 0.62)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0.276 [0.174, 0.421]</t>
+          <t>0.28 (0.10, 0.52)</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.262 [0.170, 0.361]</t>
+          <t>0.26 (0.09, 0.58)</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>0.326 [0.230, 0.442]</t>
+          <t>0.33 (0.09, 0.54)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>0.296 [0.226, 0.410]</t>
+          <t>0.30 (0.15, 0.52)</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>0.258 [0.195, 0.395]</t>
+          <t>0.26 (0.15, 0.48)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>0.309 [0.198, 0.434]</t>
+          <t>0.31 (0.11, 0.48)</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>0.230 [0.179, 0.359]</t>
+          <t>0.23 (0.07, 0.49)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>0.257 [0.210, 0.321]</t>
+          <t>0.26 (0.09, 0.57)</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>0.246 [0.209, 0.316]</t>
+          <t>0.25 (0.04, 0.62)</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0.236 [0.172, 0.332]</t>
+          <t>0.24 (0.08, 0.52)</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>0.238 [0.169, 0.315]</t>
+          <t>0.24 (0.09, 0.58)</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>0.273 [0.226, 0.395]</t>
+          <t>0.27 (0.09, 0.54)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>0.258 [0.193, 0.347]</t>
+          <t>0.26 (0.11, 0.52)</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>0.248 [0.179, 0.345]</t>
+          <t>0.25 (0.11, 0.48)</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>0.223 [0.182, 0.319]</t>
+          <t>0.22 (0.11, 0.48)</t>
         </is>
       </c>
     </row>
@@ -6568,37 +6568,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0.946 (0.883)</t>
+          <t>0.95 (0.88)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.910 (0.589)</t>
+          <t>0.91 (0.59)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.745 (0.328)</t>
+          <t>0.75 (0.33)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.847 (0.355)</t>
+          <t>0.85 (0.35)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.987 (0.358)</t>
+          <t>0.99 (0.36)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.18 (0.456)</t>
+          <t>1.18 (0.46)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.45 (0.725)</t>
+          <t>1.45 (0.72)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6613,37 +6613,37 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.02 (0.776)</t>
+          <t>1.02 (0.78)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0.951 (0.778)</t>
+          <t>0.95 (0.78)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1.00 (0.787)</t>
+          <t>1.00 (0.79)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>1.10 (0.817)</t>
+          <t>1.10 (0.82)</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>1.22 (0.932)</t>
+          <t>1.22 (0.93)</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1.50 (0.983)</t>
+          <t>1.50 (0.98)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>1.49 (0.978)</t>
+          <t>1.49 (0.98)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6658,37 +6658,37 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>0.981 (0.824)</t>
+          <t>0.98 (0.82)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>0.932 (0.688)</t>
+          <t>0.93 (0.69)</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>0.876 (0.614)</t>
+          <t>0.88 (0.61)</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>0.977 (0.645)</t>
+          <t>0.98 (0.64)</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>1.11 (0.719)</t>
+          <t>1.11 (0.72)</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>1.35 (0.786)</t>
+          <t>1.35 (0.79)</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>1.47 (0.856)</t>
+          <t>1.47 (0.86)</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6705,142 +6705,142 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.639 [0.539, 0.903]</t>
+          <t>0.64 (0.19, 4.47)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.769 [0.552, 1.13]</t>
+          <t>0.77 (0.25, 2.88)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.760 [0.542, 0.907]</t>
+          <t>0.76 (0.23, 1.32)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.820 [0.658, 1.01]</t>
+          <t>0.82 (0.24, 1.55)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.914 [0.801, 1.17]</t>
+          <t>0.91 (0.37, 1.82)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.07 [0.832, 1.41]</t>
+          <t>1.07 (0.42, 2.15)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.35 [0.986, 1.65]</t>
+          <t>1.35 (0.39, 3.74)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.23 [1.01, 2.08]</t>
+          <t>1.23 (0.77, 7.33)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1.18 [0.911, 1.65]</t>
+          <t>1.18 (0.45, 6.35)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0.776 [0.441, 1.44]</t>
+          <t>0.78 (0.35, 3.06)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0.736 [0.423, 0.987]</t>
+          <t>0.74 (0.24, 3.03)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>0.773 [0.445, 1.29]</t>
+          <t>0.77 (0.20, 3.10)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>0.817 [0.528, 1.49]</t>
+          <t>0.82 (0.22, 3.25)</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0.934 [0.562, 1.60]</t>
+          <t>0.93 (0.25, 3.65)</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>1.28 [0.812, 2.02]</t>
+          <t>1.28 (0.49, 4.00)</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1.11 [0.889, 1.91]</t>
+          <t>1.11 (0.35, 4.42)</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1.33 [0.965, 2.16]</t>
+          <t>1.33 (0.28, 4.58)</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1.43 [1.09, 2.22]</t>
+          <t>1.43 (0.24, 4.78)</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>0.688 [0.516, 1.11]</t>
+          <t>0.69 (0.19, 4.47)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>0.767 [0.464, 1.06]</t>
+          <t>0.77 (0.24, 3.03)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>0.773 [0.464, 1.03]</t>
+          <t>0.77 (0.20, 3.10)</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>0.818 [0.552, 1.10]</t>
+          <t>0.82 (0.22, 3.25)</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>0.924 [0.662, 1.31]</t>
+          <t>0.92 (0.25, 3.65)</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>1.13 [0.810, 1.70]</t>
+          <t>1.13 (0.42, 4.00)</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>1.22 [0.913, 1.75]</t>
+          <t>1.22 (0.35, 4.42)</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>1.28 [1.01, 2.16]</t>
+          <t>1.28 (0.28, 7.33)</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>1.31 [0.995, 1.90]</t>
+          <t>1.31 (0.24, 6.35)</t>
         </is>
       </c>
     </row>
@@ -7001,279 +7001,279 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>57400 (22100)</t>
+          <t>57408.40 (22058.21)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>55700 (21300)</t>
+          <t>55737.40 (21335.64)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>57200 (21000)</t>
+          <t>57232.63 (20969.10)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>61300 (22800)</t>
+          <t>61298.87 (22774.66)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>63300 (24100)</t>
+          <t>63253.99 (24144.63)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>62400 (23100)</t>
+          <t>62380.40 (23107.31)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>55700 (21000)</t>
+          <t>55733.87 (21041.55)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>54300 (20400)</t>
+          <t>54257.44 (20410.11)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>53700 (19600)</t>
+          <t>53661.90 (19627.80)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>53300 (14100)</t>
+          <t>53251.36 (14134.16)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>55200 (14100)</t>
+          <t>55190.93 (14130.90)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>54800 (12600)</t>
+          <t>54776.93 (12616.43)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>57700 (13000)</t>
+          <t>57725.88 (13014.54)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>59500 (13200)</t>
+          <t>59461.73 (13221.26)</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>59900 (13600)</t>
+          <t>59870.25 (13635.71)</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>53800 (13000)</t>
+          <t>53843.52 (13047.27)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>55500 (13100)</t>
+          <t>55510.35 (13120.71)</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>54600 (13000)</t>
+          <t>54621.98 (12979.53)</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>55300 (18400)</t>
+          <t>55329.88 (18438.00)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>55500 (17900)</t>
+          <t>55464.16 (17895.41)</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>56000 (17200)</t>
+          <t>56004.78 (17155.92)</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>59500 (18300)</t>
+          <t>59472.67 (18316.82)</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>61300 (19200)</t>
+          <t>61315.72 (19217.40)</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>61100 (18700)</t>
+          <t>61096.14 (18677.23)</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>54800 (17300)</t>
+          <t>54788.70 (17328.46)</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>54900 (16800)</t>
+          <t>54912.37 (16799.81)</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>54200 (16200)</t>
+          <t>54175.43 (16209.87)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>51400 [40400, 71000]</t>
+          <t>51353.19 (31298.35, 110315.04)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>49700 [39200, 60100]</t>
+          <t>49739.29 (34816.17, 105916.53)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>50700 [41800, 62500]</t>
+          <t>50708.06 (35794.82, 109247.75)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>55400 [44000, 69300]</t>
+          <t>55388.82 (36093.86, 115960.52)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>58400 [45200, 72000]</t>
+          <t>58433.08 (38357.93, 120045.46)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>60000 [44200, 73400]</t>
+          <t>60049.61 (38010.40, 116408.66)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>50500 [39600, 62700]</t>
+          <t>50518.38 (33755.22, 109695.79)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>48400 [39000, 62200]</t>
+          <t>48427.68 (31203.81, 106057.98)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>50000 [39600, 61200]</t>
+          <t>49983.28 (33279.64, 104294.80)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>53400 [42700, 59200]</t>
+          <t>53367.83 (23273.96, 82777.54)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>56400 [43300, 60200]</t>
+          <t>56365.96 (36208.55, 84131.80)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>56200 [44700, 58700]</t>
+          <t>56209.17 (36560.31, 79272.47)</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>57900 [47500, 64000]</t>
+          <t>57886.90 (40895.17, 90593.39)</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>58500 [49100, 66700]</t>
+          <t>58534.27 (40307.74, 89256.96)</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>60100 [50100, 66500]</t>
+          <t>60050.45 (40695.53, 88321.77)</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>51600 [44600, 58200]</t>
+          <t>51642.05 (37647.23, 83385.42)</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>57200 [46100, 59500]</t>
+          <t>57171.91 (35594.35, 82991.68)</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>54900 [45200, 59800]</t>
+          <t>54946.58 (36906.22, 82054.69)</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>52900 [40300, 59700]</t>
+          <t>52864.39 (23273.96, 110315.04)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>51800 [41500, 60600]</t>
+          <t>51805.16 (34816.17, 105916.53)</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>54800 [42600, 59600]</t>
+          <t>54835.39 (35794.82, 109247.75)</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>57300 [44300, 66300]</t>
+          <t>57327.65 (36093.86, 115960.52)</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>58500 [47200, 67700]</t>
+          <t>58534.27 (38357.93, 120045.46)</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>60000 [45600, 68600]</t>
+          <t>60049.61 (38010.40, 116408.66)</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>50900 [41400, 60000]</t>
+          <t>50880.53 (33755.22, 109695.79)</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>53600 [40800, 60100]</t>
+          <t>53634.07 (31203.81, 106057.98)</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>52700 [41200, 60900]</t>
+          <t>52658.57 (33279.64, 104294.80)</t>
         </is>
       </c>
     </row>
@@ -7434,279 +7434,279 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0.400 (0.199)</t>
+          <t>0.40 (0.20)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.397 (0.203)</t>
+          <t>0.40 (0.20)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.398 (0.208)</t>
+          <t>0.40 (0.21)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.394 (0.195)</t>
+          <t>0.39 (0.19)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.347 (0.178)</t>
+          <t>0.35 (0.18)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.345 (0.174)</t>
+          <t>0.35 (0.17)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.443 (0.207)</t>
+          <t>0.44 (0.21)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.493 (0.262)</t>
+          <t>0.49 (0.26)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.463 (0.217)</t>
+          <t>0.46 (0.22)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.471 (0.469)</t>
+          <t>0.47 (0.47)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0.433 (0.440)</t>
+          <t>0.43 (0.44)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0.464 (0.458)</t>
+          <t>0.46 (0.46)</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0.429 (0.399)</t>
+          <t>0.43 (0.40)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.406 (0.371)</t>
+          <t>0.41 (0.37)</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0.398 (0.385)</t>
+          <t>0.40 (0.38)</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>0.418 (0.363)</t>
+          <t>0.42 (0.36)</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>0.475 (0.401)</t>
+          <t>0.47 (0.40)</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>0.461 (0.406)</t>
+          <t>0.46 (0.41)</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>0.436 (0.361)</t>
+          <t>0.44 (0.36)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>0.415 (0.342)</t>
+          <t>0.42 (0.34)</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>0.431 (0.353)</t>
+          <t>0.43 (0.35)</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>0.413 (0.315)</t>
+          <t>0.41 (0.32)</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>0.377 (0.289)</t>
+          <t>0.38 (0.29)</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>0.373 (0.301)</t>
+          <t>0.37 (0.30)</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>0.429 (0.298)</t>
+          <t>0.43 (0.30)</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>0.484 (0.340)</t>
+          <t>0.48 (0.34)</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>0.462 (0.328)</t>
+          <t>0.46 (0.33)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0.367 [0.234, 0.516]</t>
+          <t>0.37 (0.10, 0.80)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.313 [0.267, 0.555]</t>
+          <t>0.31 (0.13, 0.82)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.315 [0.248, 0.543]</t>
+          <t>0.32 (0.14, 0.91)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.335 [0.255, 0.466]</t>
+          <t>0.33 (0.13, 0.84)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.296 [0.230, 0.391]</t>
+          <t>0.30 (0.12, 0.79)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.292 [0.228, 0.435]</t>
+          <t>0.29 (0.12, 0.75)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.357 [0.326, 0.555]</t>
+          <t>0.36 (0.12, 0.91)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.414 [0.305, 0.627]</t>
+          <t>0.41 (0.13, 1.02)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.408 [0.309, 0.525]</t>
+          <t>0.41 (0.20, 0.89)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0.263 [0.203, 0.356]</t>
+          <t>0.26 (0.15, 1.70)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0.261 [0.206, 0.347]</t>
+          <t>0.26 (0.16, 1.69)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0.295 [0.212, 0.359]</t>
+          <t>0.29 (0.15, 1.78)</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>0.292 [0.196, 0.370]</t>
+          <t>0.29 (0.13, 1.63)</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.262 [0.198, 0.355]</t>
+          <t>0.26 (0.13, 1.55)</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>0.269 [0.188, 0.371]</t>
+          <t>0.27 (0.12, 1.62)</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>0.290 [0.219, 0.394]</t>
+          <t>0.29 (0.13, 1.57)</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>0.330 [0.214, 0.559]</t>
+          <t>0.33 (0.14, 1.67)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>0.286 [0.234, 0.455]</t>
+          <t>0.29 (0.14, 1.66)</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>0.310 [0.216, 0.502]</t>
+          <t>0.31 (0.10, 1.70)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>0.287 [0.221, 0.426]</t>
+          <t>0.29 (0.13, 1.69)</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>0.312 [0.229, 0.499]</t>
+          <t>0.31 (0.14, 1.78)</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>0.306 [0.236, 0.429]</t>
+          <t>0.31 (0.13, 1.63)</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>0.285 [0.216, 0.389]</t>
+          <t>0.28 (0.12, 1.55)</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>0.269 [0.208, 0.410]</t>
+          <t>0.27 (0.12, 1.62)</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>0.347 [0.239, 0.519]</t>
+          <t>0.35 (0.12, 1.57)</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>0.383 [0.252, 0.593]</t>
+          <t>0.38 (0.13, 1.67)</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>0.355 [0.265, 0.512]</t>
+          <t>0.36 (0.14, 1.66)</t>
         </is>
       </c>
     </row>
@@ -7872,274 +7872,274 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>4.25 (11.1)</t>
+          <t>4.25 (11.07)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.04 (10.6)</t>
+          <t>4.04 (10.56)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>4.12 (10.6)</t>
+          <t>4.12 (10.56)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4.27 (10.8)</t>
+          <t>4.27 (10.81)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4.84 (12.4)</t>
+          <t>4.84 (12.36)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.13 (10.4)</t>
+          <t>4.13 (10.36)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4.23 (10.7)</t>
+          <t>4.23 (10.73)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4.17 (10.5)</t>
+          <t>4.17 (10.47)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>6.17 (15.4)</t>
+          <t>6.17 (15.45)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>6.52 (16.2)</t>
+          <t>6.52 (16.23)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>6.22 (15.4)</t>
+          <t>6.22 (15.42)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>6.33 (15.8)</t>
+          <t>6.33 (15.79)</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>6.78 (16.6)</t>
+          <t>6.78 (16.61)</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>7.04 (16.7)</t>
+          <t>7.04 (16.73)</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>6.16 (15.2)</t>
+          <t>6.16 (15.16)</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>6.07 (15.1)</t>
+          <t>6.07 (15.08)</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>6.15 (15.2)</t>
+          <t>6.15 (15.20)</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>5.07 (12.9)</t>
+          <t>5.07 (12.94)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>5.44 (13.9)</t>
+          <t>5.44 (13.90)</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>5.15 (13.2)</t>
+          <t>5.15 (13.17)</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>5.27 (13.4)</t>
+          <t>5.27 (13.44)</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>5.55 (14.0)</t>
+          <t>5.55 (13.97)</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>6.02 (14.7)</t>
+          <t>6.02 (14.73)</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>5.19 (13.0)</t>
+          <t>5.19 (12.98)</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>5.23 (13.2)</t>
+          <t>5.23 (13.17)</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>5.23 (13.1)</t>
+          <t>5.23 (13.10)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.56 [1.21, 2.59]</t>
+          <t>1.56 (0.81, 48.17)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.56 [1.28, 2.32]</t>
+          <t>1.56 (0.92, 51.18)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.61 [1.29, 2.36]</t>
+          <t>1.61 (0.91, 51.20)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.71 [1.30, 2.34]</t>
+          <t>1.71 (0.97, 50.10)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.75 [1.40, 2.43]</t>
+          <t>1.75 (1.05, 51.32)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.89 [1.39, 2.42]</t>
+          <t>1.89 (1.13, 54.32)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.70 [1.35, 2.34]</t>
+          <t>1.70 (1.05, 49.28)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.71 [1.31, 2.21]</t>
+          <t>1.71 (1.02, 48.45)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1.61 [1.34, 2.26]</t>
+          <t>1.61 (0.96, 47.32)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1.50 [1.11, 1.87]</t>
+          <t>1.50 (0.44, 55.95)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1.40 [1.21, 1.86]</t>
+          <t>1.40 (0.56, 60.55)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1.48 [1.27, 1.86]</t>
+          <t>1.48 (0.62, 57.41)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>1.54 [1.27, 1.92]</t>
+          <t>1.54 (0.64, 59.51)</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>1.64 [1.32, 2.02]</t>
+          <t>1.64 (0.66, 58.80)</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>1.71 [1.28, 2.22]</t>
+          <t>1.71 (0.77, 57.79)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>1.59 [1.15, 2.13]</t>
+          <t>1.59 (0.68, 57.65)</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1.55 [1.18, 1.91]</t>
+          <t>1.55 (0.70, 58.08)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1.45 [1.18, 1.72]</t>
+          <t>1.45 (0.67, 57.96)</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1.51 [1.15, 2.17]</t>
+          <t>1.51 (0.44, 55.95)</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>1.53 [1.26, 1.91]</t>
+          <t>1.53 (0.56, 60.55)</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>1.60 [1.29, 2.02]</t>
+          <t>1.60 (0.62, 57.41)</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>1.58 [1.28, 2.12]</t>
+          <t>1.58 (0.64, 59.51)</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>1.73 [1.35, 2.29]</t>
+          <t>1.73 (0.66, 58.80)</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>1.71 [1.32, 2.36]</t>
+          <t>1.71 (0.77, 57.79)</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>1.62 [1.23, 2.33]</t>
+          <t>1.62 (0.68, 57.65)</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1.60 [1.26, 2.06]</t>
+          <t>1.60 (0.70, 58.08)</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>1.50 [1.23, 1.99]</t>
+          <t>1.50 (0.67, 57.96)</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0.811 (0.997)</t>
+          <t>0.81 (1.00)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.899 (1.28)</t>
+          <t>0.90 (1.28)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.918 (1.32)</t>
+          <t>0.92 (1.32)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.869 (1.23)</t>
+          <t>0.87 (1.23)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0.879 (0.975)</t>
+          <t>0.88 (0.97)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>0.995 (1.44)</t>
+          <t>1.00 (1.44)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>0.947 (1.26)</t>
+          <t>0.95 (1.26)</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>0.988 (1.21)</t>
+          <t>0.99 (1.21)</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8437,142 +8437,142 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0.583 [0.198, 0.631]</t>
+          <t>0.58 (0.10, 2.54)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.827 [0.677, 1.93]</t>
+          <t>0.83 (0.53, 3.03)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.264 [0.251, 0.912]</t>
+          <t>0.26 (0.25, 2.82)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.594 [0.501, 1.95]</t>
+          <t>0.59 (0.41, 3.30)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3.25 [3.25, 3.25]</t>
+          <t>3.25 (3.25, 3.25)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.472 [0.173, 0.709]</t>
+          <t>0.47 (0.01, 3.22)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.303 [0.168, 1.00]</t>
+          <t>0.30 (0.16, 2.71)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.565 [0.421, 0.610]</t>
+          <t>0.57 (0.20, 2.60)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2.52 [2.52, 2.52]</t>
+          <t>2.52 (2.52, 2.52)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>3.12 [3.12, 3.12]</t>
+          <t>3.12 (3.12, 3.12)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0.671 [0.342, 1.46]</t>
+          <t>0.67 (0.13, 3.06)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0.363 [0.300, 1.06]</t>
+          <t>0.36 (0.11, 3.14)</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>0.459 [0.265, 1.44]</t>
+          <t>0.46 (0.23, 3.85)</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0.761 [0.522, 2.06]</t>
+          <t>0.76 (0.28, 3.35)</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>1.88 [1.37, 2.39]</t>
+          <t>1.88 (0.86, 2.91)</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>0.565 [0.339, 1.33]</t>
+          <t>0.56 (0.18, 3.12)</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1.94 [1.47, 2.41]</t>
+          <t>1.94 (1.00, 2.88)</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1.73 [1.03, 2.42]</t>
+          <t>1.73 (0.34, 3.12)</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>0.607 [0.294, 2.07]</t>
+          <t>0.61 (0.10, 3.12)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>0.827 [0.470, 1.98]</t>
+          <t>0.83 (0.13, 3.06)</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>0.320 [0.251, 0.977]</t>
+          <t>0.32 (0.11, 3.14)</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>0.594 [0.342, 1.97]</t>
+          <t>0.59 (0.23, 3.85)</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2.01 [0.642, 3.28]</t>
+          <t>2.01 (0.28, 3.35)</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>0.709 [0.322, 1.88]</t>
+          <t>0.71 (0.01, 3.22)</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>0.414 [0.177, 1.23]</t>
+          <t>0.41 (0.16, 3.12)</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>0.610 [0.493, 1.80]</t>
+          <t>0.61 (0.20, 2.88)</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2.52 [1.43, 2.82]</t>
+          <t>2.52 (0.34, 3.12)</t>
         </is>
       </c>
     </row>
@@ -8733,279 +8733,279 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16.0 (15.9)</t>
+          <t>16.01 (15.88)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>14.8 (13.5)</t>
+          <t>14.81 (13.50)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16.8 (16.0)</t>
+          <t>16.76 (15.99)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18.8 (18.0)</t>
+          <t>18.75 (17.99)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18.4 (17.4)</t>
+          <t>18.39 (17.38)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18.5 (18.2)</t>
+          <t>18.48 (18.16)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>15.4 (14.6)</t>
+          <t>15.36 (14.60)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>16.6 (14.5)</t>
+          <t>16.60 (14.53)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>18.0 (15.1)</t>
+          <t>17.98 (15.13)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>13.2 (14.0)</t>
+          <t>13.16 (13.99)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>14.1 (14.8)</t>
+          <t>14.05 (14.77)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>13.7 (14.8)</t>
+          <t>13.65 (14.81)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>13.8 (14.4)</t>
+          <t>13.84 (14.40)</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>13.8 (14.2)</t>
+          <t>13.81 (14.16)</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>14.6 (15.2)</t>
+          <t>14.65 (15.18)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>12.8 (14.0)</t>
+          <t>12.79 (14.05)</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>12.3 (13.2)</t>
+          <t>12.27 (13.25)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>12.2 (13.8)</t>
+          <t>12.22 (13.76)</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>14.6 (14.8)</t>
+          <t>14.55 (14.84)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>14.4 (14.0)</t>
+          <t>14.41 (14.01)</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>15.2 (15.3)</t>
+          <t>15.17 (15.31)</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>16.2 (16.2)</t>
+          <t>16.18 (16.21)</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>16.0 (15.8)</t>
+          <t>16.00 (15.76)</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>16.5 (16.6)</t>
+          <t>16.47 (16.56)</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14.0 (14.2)</t>
+          <t>13.98 (14.19)</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>14.3 (13.9)</t>
+          <t>14.28 (13.86)</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14.8 (14.5)</t>
+          <t>14.81 (14.50)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Median [Q1, Q3]</t>
+          <t xml:space="preserve">  Median (Min, Max)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8.58 [5.78, 19.7]</t>
+          <t>8.58 (1.28, 54.97)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9.30 [5.34, 16.9]</t>
+          <t>9.30 (1.29, 48.38)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9.69 [5.80, 19.4]</t>
+          <t>9.69 (1.43, 61.53)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>11.6 [6.14, 21.9]</t>
+          <t>11.56 (1.55, 66.74)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>11.1 [5.41, 21.7]</t>
+          <t>11.08 (1.34, 64.03)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>10.0 [5.06, 27.4]</t>
+          <t>10.00 (1.73, 62.90)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>9.69 [5.08, 17.0]</t>
+          <t>9.69 (1.42, 55.62)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10.4 [7.44, 23.4]</t>
+          <t>10.44 (1.64, 51.63)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>11.2 [8.24, 29.3]</t>
+          <t>11.23 (3.73, 53.72)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>7.09 [5.21, 17.1]</t>
+          <t>7.09 (1.45, 59.55)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>7.06 [5.50, 18.3]</t>
+          <t>7.06 (2.24, 62.05)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>7.06 [5.22, 17.5]</t>
+          <t>7.06 (2.18, 63.52)</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>7.74 [5.34, 17.3]</t>
+          <t>7.74 (2.28, 59.96)</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>7.38 [5.21, 17.9]</t>
+          <t>7.38 (2.23, 58.24)</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>7.32 [5.41, 18.7]</t>
+          <t>7.32 (2.04, 60.18)</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>7.00 [4.79, 15.5]</t>
+          <t>7.00 (1.86, 58.92)</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>6.57 [4.54, 16.5]</t>
+          <t>6.57 (2.00, 57.55)</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>6.23 [4.33, 16.1]</t>
+          <t>6.23 (1.69, 59.99)</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>8.39 [5.54, 19.3]</t>
+          <t>8.39 (1.28, 59.55)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>8.78 [5.48, 18.3]</t>
+          <t>8.78 (1.29, 62.05)</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>8.48 [5.37, 19.7]</t>
+          <t>8.48 (1.43, 63.52)</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>9.71 [5.88, 19.4]</t>
+          <t>9.71 (1.55, 66.74)</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>9.50 [5.27, 18.9]</t>
+          <t>9.50 (1.34, 64.03)</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>9.52 [5.31, 19.9]</t>
+          <t>9.52 (1.73, 62.90)</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>8.70 [4.83, 16.6]</t>
+          <t>8.70 (1.42, 58.92)</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>8.87 [4.87, 19.2]</t>
+          <t>8.87 (1.64, 57.55)</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>9.00 [4.56, 18.8]</t>
+          <t>9.00 (1.69, 59.99)</t>
         </is>
       </c>
     </row>
